--- a/DOSSIES_MULTIFORMATO/DPE/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/DPE/dossie.xlsx
@@ -628,7 +628,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2023NE02004</t>
+          <t>2023NE0002004</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -651,14 +651,14 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PRODAM RH - ESTAGIARIOS</t>
+          <t>Contrato nº 32/2023, a ser celebrado entre Defensoria Pública do Estado do Amazonas-DPE/AM e a PRODAM - Processamento de Dados Amazonas S.A. Controle de cadastro de pessoal (Estagiários).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023NE0002004</t>
+          <t>2023NE02004</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -681,19 +681,19 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Contrato nº 32/2023, a ser celebrado entre Defensoria Pública do Estado do Amazonas-DPE/AM e a PRODAM - Processamento de Dados Amazonas S.A. Controle de cadastro de pessoal (Estagiários).</t>
+          <t>PRODAM RH - ESTAGIARIOS</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2014NE00120</t>
+          <t>2014NE00121</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5/2014</t>
+          <t>4/2014</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>29410.75</v>
+        <v>403412.58</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -711,19 +711,19 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Contrato No. 5/2014 - CFPP - Cad.e Folha de Pagto. De Pessoal</t>
+          <t>Contrato No. 4/2014 - Hospedagem de servidor, Internet, Firewall e Transmis. De dados</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2014NE00121</t>
+          <t>2014NE00120</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4/2014</t>
+          <t>5/2014</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>403412.58</v>
+        <v>29410.75</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -741,24 +741,28 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Contrato No. 4/2014 - Hospedagem de servidor, Internet, Firewall e Transmis. De dados</t>
+          <t>Contrato No. 5/2014 - CFPP - Cad.e Folha de Pagto. De Pessoal</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023NE0002338</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>2023NE0002341</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>32/2023</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>30/08/2023</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>25746.74</v>
+        <v>21497.04</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -767,28 +771,24 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CANCELAMENTO DA NOTA DE EMPENHO Nº 2004/2023 EM RAZÃO DE AJUSTE NO CRONOGRAMA DE PAGAMENTO DO CONTRATO Nº 32/2023. CONFORME DESPACHO Nº 2061/2023-DACC-DPE/AM - PROC. SEI Nº 5556-5/23.</t>
+          <t>Contratação de empresa para prestação de Serviço de Implantação de Sistemas de Informação e Execução de Sistemas PRODAM-RH.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023NE0002341</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>32/2023</t>
-        </is>
-      </c>
+          <t>2023NE0002338</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>30/08/2023</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>21497.04</v>
+        <v>25746.74</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação de Serviço de Implantação de Sistemas de Informação e Execução de Sistemas PRODAM-RH.</t>
+          <t>CANCELAMENTO DA NOTA DE EMPENHO Nº 2004/2023 EM RAZÃO DE AJUSTE NO CRONOGRAMA DE PAGAMENTO DO CONTRATO Nº 32/2023. CONFORME DESPACHO Nº 2061/2023-DACC-DPE/AM - PROC. SEI Nº 5556-5/23.</t>
         </is>
       </c>
     </row>
@@ -1062,12 +1062,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025NE0000712</t>
+          <t>2025NE0000719</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>17/2024</t>
+          <t>32/2023</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1076,7 +1076,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>22378.72</v>
+        <v>18534.8</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1085,19 +1085,19 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de execução e desenvolvimento de sistemas, contemplando a execução de sistema de informação para disponibilização do Sistema de Controle de Material e Patrimônio - AJURI, em p</t>
+          <t>Atender despesas com 1º Termo Aditivo ao contrato nº Contrato nº 32/2023, a ser celebrado entre Defensoria Pública do Estado do Amazonas-DPE/AM e a PRODAM - Processamento de Dados Amazonas S.A.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025NE0000719</t>
+          <t>2025NE0000712</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>32/2023</t>
+          <t>17/2024</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1106,7 +1106,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>18534.8</v>
+        <v>22378.72</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1115,14 +1115,14 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Atender despesas com 1º Termo Aditivo ao contrato nº Contrato nº 32/2023, a ser celebrado entre Defensoria Pública do Estado do Amazonas-DPE/AM e a PRODAM - Processamento de Dados Amazonas S.A.</t>
+          <t>Contratação dos serviços de execução e desenvolvimento de sistemas, contemplando a execução de sistema de informação para disponibilização do Sistema de Controle de Material e Patrimônio - AJURI, em p</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2023NE00717</t>
+          <t>2023NE0000717</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1145,14 +1145,14 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Execução de Sistema PRODAM RH</t>
+          <t>Contrato nº 12/2023-DPE-AM, a ser celebrado entre a Defensoria Pública do Estado do Amazonas-DPE/AM, e a Empresa Prodam Processamento de Dados Amazonas-Prodam/AM; Sistemas PRODAM-RH.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2023NE0000717</t>
+          <t>2023NE00717</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1175,19 +1175,19 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Contrato nº 12/2023-DPE-AM, a ser celebrado entre a Defensoria Pública do Estado do Amazonas-DPE/AM, e a Empresa Prodam Processamento de Dados Amazonas-Prodam/AM; Sistemas PRODAM-RH.</t>
+          <t>Execução de Sistema PRODAM RH</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2015NE00149</t>
+          <t>2015NE00152</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4/2014</t>
+          <t>13/2014</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>336177.15</v>
+        <v>17122.98</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1205,19 +1205,19 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE ACESSO À INTERNET, Descrição: Contratação de Pessoa Jurídica especializada em serviço de banda larga de acesso a internet e circuito de comunicação de dados via fibra óptica, com locação t</t>
+          <t xml:space="preserve">contratação de empresa especializada na prestação de serviço de informática para implantação de Sistema de Controle de Material e Patrimônio - AJURI, conforme projeto básico MARCA: prodam Contrato nº </t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2015NE00152</t>
+          <t>2015NE00149</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13/2014</t>
+          <t>4/2014</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>17122.98</v>
+        <v>336177.15</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1235,28 +1235,24 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">contratação de empresa especializada na prestação de serviço de informática para implantação de Sistema de Controle de Material e Patrimônio - AJURI, conforme projeto básico MARCA: prodam Contrato nº </t>
+          <t>SERVIÇOS DE ACESSO À INTERNET, Descrição: Contratação de Pessoa Jurídica especializada em serviço de banda larga de acesso a internet e circuito de comunicação de dados via fibra óptica, com locação t</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026NE0000163</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>18/2025</t>
-        </is>
-      </c>
+          <t>2026NE0000142</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
           <t>23/01/2026</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>6647.45</v>
+        <v>3421.42</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1265,19 +1261,19 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atender despesas de exercício anterior, decorrente da anulação do empenho original nº 2025NE0001270, referente ao período de novembro e dezembro/2025.</t>
+          <t>Anulação erro da natureza</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026NE0000139</t>
+          <t>2026NE0000206</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>17/2024</t>
+          <t>6/2025</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1286,7 +1282,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3421.42</v>
+        <v>47601.64</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1295,21 +1291,17 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Atender despesas de exercício anterior, decorrente da anulação do empenho original nº 2025NE0000048, referente ao período de novembro/2025.</t>
+          <t>Atender despesas de exercício anterior, decorrente da anulação do empenho original nº 2025NE0000603.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026NE0000143</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>17/2024</t>
-        </is>
-      </c>
+          <t>2026NE0000238</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
           <t>23/01/2026</t>
@@ -1325,17 +1317,21 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Atender despesas de exercício anterior, decorrente da anulação do empenho original nº 2025NE0000048, referente ao período de novembro/2025.</t>
+          <t>Atender despesas de exercício anterior, decorrente da anulação do empenho original nº 2025NE0001975.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026NE0000238</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
+          <t>2026NE0000143</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>17/2024</t>
+        </is>
+      </c>
       <c r="C26" t="inlineStr">
         <is>
           <t>23/01/2026</t>
@@ -1351,19 +1347,19 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Atender despesas de exercício anterior, decorrente da anulação do empenho original nº 2025NE0001975.</t>
+          <t>Atender despesas de exercício anterior, decorrente da anulação do empenho original nº 2025NE0000048, referente ao período de novembro/2025.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026NE0000206</t>
+          <t>2026NE0000139</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>6/2025</t>
+          <t>17/2024</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1372,7 +1368,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>47601.64</v>
+        <v>3421.42</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1381,24 +1377,28 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atender despesas de exercício anterior, decorrente da anulação do empenho original nº 2025NE0000603.</t>
+          <t>Atender despesas de exercício anterior, decorrente da anulação do empenho original nº 2025NE0000048, referente ao período de novembro/2025.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026NE0000142</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
+          <t>2026NE0000163</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>18/2025</t>
+        </is>
+      </c>
       <c r="C28" t="inlineStr">
         <is>
           <t>23/01/2026</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>3421.42</v>
+        <v>6647.45</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1407,14 +1407,14 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Anulação erro da natureza</t>
+          <t>Atender despesas de exercício anterior, decorrente da anulação do empenho original nº 2025NE0001270, referente ao período de novembro e dezembro/2025.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025NE0002401</t>
+          <t>2025NE0002427</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6737.83</v>
+        <v>3421.42</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025NE0002350</t>
+          <t>2025NE0002443</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>36122.03</v>
+        <v>11479.61</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1459,14 +1459,14 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Em virtude do encerramento do exercício de 2025.</t>
+          <t>ENCERRAMENTO DO EXERCÍCIO</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025NE0002426</t>
+          <t>2025NE0002424</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3421.42</v>
+        <v>4249.7</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025NE0002424</t>
+          <t>2025NE0002426</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>4249.7</v>
+        <v>3421.42</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025NE0002443</t>
+          <t>2025NE0002350</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11479.61</v>
+        <v>36122.03</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1537,14 +1537,14 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ENCERRAMENTO DO EXERCÍCIO</t>
+          <t>Em virtude do encerramento do exercício de 2025.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025NE0002427</t>
+          <t>2025NE0002401</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1554,7 +1554,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>3421.42</v>
+        <v>6737.83</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1622,12 +1622,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2015NE00351</t>
+          <t>2015NE00343</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>13/2014</t>
+          <t>5/2014</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1636,7 +1636,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>17676.84</v>
+        <v>532.79</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA NE N° 49/15, REFERENTE AO SALDO DO CONTRATO N° 013/2014 ¿ PRODAM - AJURI, CONFORME DESPACHO DO MEMORANDO N° 32/15 ¿ DF/DPE ¿ AM.</t>
+          <t>ANULAÇÃO PARCIAL DA NE N° 26/15, REFERENTE A SALDO DE CONTRATO N° 005/2014 ¿ PRODAM, CONFORME DESPACHO DO MEMORANDO N° 32/15 ¿ DF/DPE ¿ AM.</t>
         </is>
       </c>
     </row>
@@ -1682,12 +1682,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2015NE00343</t>
+          <t>2015NE00351</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5/2014</t>
+          <t>13/2014</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>532.79</v>
+        <v>17676.84</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA NE N° 26/15, REFERENTE A SALDO DE CONTRATO N° 005/2014 ¿ PRODAM, CONFORME DESPACHO DO MEMORANDO N° 32/15 ¿ DF/DPE ¿ AM.</t>
+          <t>ANULAÇÃO PARCIAL DA NE N° 49/15, REFERENTE AO SALDO DO CONTRATO N° 013/2014 ¿ PRODAM - AJURI, CONFORME DESPACHO DO MEMORANDO N° 32/15 ¿ DF/DPE ¿ AM.</t>
         </is>
       </c>
     </row>
@@ -2112,14 +2112,10 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2023NE0000307</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2/2018</t>
-        </is>
-      </c>
+          <t>2023NE0000308</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
           <t>08/02/2023</t>
@@ -2135,17 +2131,21 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Pagamento indenizatório referente a prestação de serviço de desenvolvimento de rotina automatizada para extração de dados do sistema PRODAMRH.</t>
+          <t>Anulação devido o pagamento ter sido efetuado através de contrato.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2023NE0000308</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
+          <t>2023NE0000307</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2/2018</t>
+        </is>
+      </c>
       <c r="C55" t="inlineStr">
         <is>
           <t>08/02/2023</t>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Anulação devido o pagamento ter sido efetuado através de contrato.</t>
+          <t>Pagamento indenizatório referente a prestação de serviço de desenvolvimento de rotina automatizada para extração de dados do sistema PRODAMRH.</t>
         </is>
       </c>
     </row>
@@ -2228,12 +2228,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026NE0000050</t>
+          <t>2026NE0000062</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>6/2025</t>
+          <t>17/2024</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2242,7 +2242,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>128079.9</v>
+        <v>37635.62</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2251,19 +2251,19 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Contrato n.º 06/2025 celebrado entre a Defensoria Pública do Estado do Amazonas e a empresa PRODAM - Processamento de Dados Amazonas S.A.</t>
+          <t>Contrato nº 17/2024 celebrado entre a Defensoria Pública do Estado do Amazonas e a empresa Prodam - Processamento de Dados Amazonas S.A, referente a contratação dos serviços de execução e desenvolvime</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026NE0000077</t>
+          <t>2026NE0000036</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1/2026</t>
+          <t>18/2025</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2272,7 +2272,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>62764</v>
+        <v>26728</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2281,19 +2281,19 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Contrato n.º 01/2026 celebrado entre a Defensoria Pública do Estado do Amazonas e Processamento de Dados Amazonas S.A - PRODAM.</t>
+          <t>Contrato n.º 18/2025 celebrado entre a Defensoria Pública do Estado do Amazonas e Processamento de Dados Amazonas S.A - PRODAM, referente a contratação de empresa especializada para fornecimento de so</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026NE0000036</t>
+          <t>2026NE0000077</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>18/2025</t>
+          <t>1/2026</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2302,7 +2302,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>26728</v>
+        <v>62764</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2311,19 +2311,19 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Contrato n.º 18/2025 celebrado entre a Defensoria Pública do Estado do Amazonas e Processamento de Dados Amazonas S.A - PRODAM, referente a contratação de empresa especializada para fornecimento de so</t>
+          <t>Contrato n.º 01/2026 celebrado entre a Defensoria Pública do Estado do Amazonas e Processamento de Dados Amazonas S.A - PRODAM.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026NE0000062</t>
+          <t>2026NE0000050</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>17/2024</t>
+          <t>6/2025</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>37635.62</v>
+        <v>128079.9</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2341,19 +2341,19 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Contrato nº 17/2024 celebrado entre a Defensoria Pública do Estado do Amazonas e a empresa Prodam - Processamento de Dados Amazonas S.A, referente a contratação dos serviços de execução e desenvolvime</t>
+          <t>Contrato n.º 06/2025 celebrado entre a Defensoria Pública do Estado do Amazonas e a empresa PRODAM - Processamento de Dados Amazonas S.A.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2015NE00049</t>
+          <t>2015NE00036</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>13/2014</t>
+          <t>4/2014</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2362,7 +2362,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>9784.559999999999</v>
+        <v>268941.72</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2408,12 +2408,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2015NE00036</t>
+          <t>2015NE00049</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>4/2014</t>
+          <t>13/2014</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>268941.72</v>
+        <v>9784.559999999999</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2438,12 +2438,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2022NE0001860</t>
+          <t>2022NE01858</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>174/2022</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2452,7 +2452,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>2628.77</v>
+        <v>1416.35</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>3º Termo de Apostilamento ao Contrato nº 011/2019, celebrado entre a Defensoria Pública do Estado do Amazonas-DPE/AM e a PRODAM -Processamento de Dados Amazonas S.A que tem como objeto a prorrogação d</t>
+          <t>Cobertura Financeira</t>
         </is>
       </c>
     </row>
@@ -2498,12 +2498,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2022NE01858</t>
+          <t>2022NE0001860</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>174/2022</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1416.35</v>
+        <v>2628.77</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2521,19 +2521,19 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Cobertura Financeira</t>
+          <t>3º Termo de Apostilamento ao Contrato nº 011/2019, celebrado entre a Defensoria Pública do Estado do Amazonas-DPE/AM e a PRODAM -Processamento de Dados Amazonas S.A que tem como objeto a prorrogação d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2022NE0000035</t>
+          <t>2022NE0000052</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>2/2018</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2542,7 +2542,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>26268.57</v>
+        <v>11377.17</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2551,19 +2551,19 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviço de Licença de uso de sistema de informação para a disponibilização do Sistema de Controle de Material e Patrimônio - AJURI.</t>
+          <t>Atender despesas com o 4º Termo Aditivo ao Contrato nº 002/2018¿DPE-AM, celebrado entre a Defensoria Pública do Estado do Amazonas-DPE/AM e a empresa Prodam Processamento de Dados Amazonas-Prodam/AM</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2022NE0000052</t>
+          <t>2022NE0000035</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2/2018</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2572,7 +2572,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11377.17</v>
+        <v>26268.57</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Atender despesas com o 4º Termo Aditivo ao Contrato nº 002/2018¿DPE-AM, celebrado entre a Defensoria Pública do Estado do Amazonas-DPE/AM e a empresa Prodam Processamento de Dados Amazonas-Prodam/AM</t>
+          <t>Contratação de empresa especializada na prestação de serviço de Licença de uso de sistema de informação para a disponibilização do Sistema de Controle de Material e Patrimônio - AJURI.</t>
         </is>
       </c>
     </row>
@@ -2618,12 +2618,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2025NE0000073</t>
+          <t>2025NE0000028</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>32/2023</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>18534.8</v>
+        <v>25253.01</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Atender despesas com 1º Termo Aditivo ao contrato nº Contrato nº 32/2023, a ser celebrado entre Defensoria Pública do Estado do Amazonas-DPE/AM e a PRODAM - Processamento de Dados Amazonas S.A Contrat</t>
+          <t>1º Termo Aditivo ao Contrato nº 12/2023-DPE-AM, celebrado entre a Defensoria Pública do Estado do Amazonas-DPE/AM, e a Empresa Prodam Processamento de Dados Amazonas-Prodam/AM.</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2025NE0000028</t>
+          <t>2025NE0000073</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>32/2023</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2692,7 +2692,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>25253.01</v>
+        <v>18534.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2701,19 +2701,19 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1º Termo Aditivo ao Contrato nº 12/2023-DPE-AM, celebrado entre a Defensoria Pública do Estado do Amazonas-DPE/AM, e a Empresa Prodam Processamento de Dados Amazonas-Prodam/AM.</t>
+          <t>Atender despesas com 1º Termo Aditivo ao contrato nº Contrato nº 32/2023, a ser celebrado entre Defensoria Pública do Estado do Amazonas-DPE/AM e a PRODAM - Processamento de Dados Amazonas S.A Contrat</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2024NE0000020</t>
+          <t>2024NE0000046</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>32/2023</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2722,7 +2722,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>37069.6</v>
+        <v>25253.01</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2731,19 +2731,19 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Contrato nº 32/2023, a ser celebrado entre Defensoria Pública do Estado do Amazonas-DPE/AM e a PRODAM - Processamento de Dados Amazonas S.A.</t>
+          <t>Contrato nº 12/2023-DPE-AM, celebrado entre a Defensoria Pública do Estado do Amazonas-DPE/AM, e a Empresa Prodam Processamento de Dados Amazonas-Prodam/AM;</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2024NE0000046</t>
+          <t>2024NE0000020</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>32/2023</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>25253.01</v>
+        <v>37069.6</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Contrato nº 12/2023-DPE-AM, celebrado entre a Defensoria Pública do Estado do Amazonas-DPE/AM, e a Empresa Prodam Processamento de Dados Amazonas-Prodam/AM;</t>
+          <t>Contrato nº 32/2023, a ser celebrado entre Defensoria Pública do Estado do Amazonas-DPE/AM e a PRODAM - Processamento de Dados Amazonas S.A.</t>
         </is>
       </c>
     </row>
@@ -2794,12 +2794,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2015NE00223</t>
+          <t>2015NE00219</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>4/2014</t>
+          <t>13/2014</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2808,7 +2808,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>51228.37</v>
+        <v>5000</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2817,14 +2817,14 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Cancelamento da Nota de Empenho n° 0036/2015 - PRODAM do 2º Termo Aditivo ao Contrato nº 004/2014-DPE/AM, referente a Contratação de Pessoa Jurídica especializada em serviço de banda larga de acesso a</t>
+          <t>Cancelamento da Nota de Empenho n° 0049/15, do Contrato n° 013/2014 ¿ PRODAM, referente à Contratação de Empresa Especializada na Prestação de Serviço de Informática para Implantação de Sistema de Con</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2015NE00224</t>
+          <t>2015NE00199</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2847,14 +2847,14 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Cancelamento da Nota de Empenho n°0098/2015 ¿ PRODAM do 1º Termo Aditivo ao Contrato nº 005/2014 - DPE/AM, referente a Contratação de empresa especializada na prestação de serviços de processamento do</t>
+          <t>Empenho de contrato: importado manualmente em 18/09/2015</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2015NE00199</t>
+          <t>2015NE00224</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2877,19 +2877,19 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Empenho de contrato: importado manualmente em 18/09/2015</t>
+          <t>Cancelamento da Nota de Empenho n°0098/2015 ¿ PRODAM do 1º Termo Aditivo ao Contrato nº 005/2014 - DPE/AM, referente a Contratação de empresa especializada na prestação de serviços de processamento do</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2015NE00219</t>
+          <t>2015NE00223</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>13/2014</t>
+          <t>4/2014</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2898,7 +2898,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>5000</v>
+        <v>51228.37</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Cancelamento da Nota de Empenho n° 0049/15, do Contrato n° 013/2014 ¿ PRODAM, referente à Contratação de Empresa Especializada na Prestação de Serviço de Informática para Implantação de Sistema de Con</t>
+          <t>Cancelamento da Nota de Empenho n° 0036/2015 - PRODAM do 2º Termo Aditivo ao Contrato nº 004/2014-DPE/AM, referente a Contratação de Pessoa Jurídica especializada em serviço de banda larga de acesso a</t>
         </is>
       </c>
     </row>

--- a/DOSSIES_MULTIFORMATO/DPE/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/DPE/dossie.xlsx
@@ -577,7 +577,11 @@
           <t>data_prescricao_proxima</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2030-02-28</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
